--- a/tir_fondos.xlsx
+++ b/tir_fondos.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://balanzcapitalsa.sharepoint.com/sites/FCI/Shared Documents/General/FCI/Matias/Cartera de Fondos/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="39" documentId="8_{A13EEC8C-EB53-4E5F-A7CC-BE36694CDE73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{38FAD81A-75A5-4D35-995D-A451661AF891}"/>
+  <xr:revisionPtr revIDLastSave="55" documentId="8_{A13EEC8C-EB53-4E5F-A7CC-BE36694CDE73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F7BEB775-06C8-447A-8593-023C4E657355}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{9E9F1388-DBFD-43C1-B41D-53AD3C2134BF}"/>
   </bookViews>
   <sheets>
     <sheet name="tir_fondos" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -1062,10 +1062,10 @@
         <v>6</v>
       </c>
       <c r="C2" s="1">
-        <v>7.7000000000000002E-3</v>
+        <v>7.7999999999999996E-3</v>
       </c>
       <c r="D2" s="1">
-        <v>7.7000000000000002E-3</v>
+        <v>7.7999999999999996E-3</v>
       </c>
       <c r="E2">
         <v>0.06</v>
@@ -1079,13 +1079,13 @@
         <v>6</v>
       </c>
       <c r="C3" s="1">
-        <v>3.9313610016860512E-2</v>
+        <v>3.9117456155971286E-2</v>
       </c>
       <c r="D3" s="1">
-        <v>3.9699999999999999E-2</v>
+        <v>3.95E-2</v>
       </c>
       <c r="E3">
-        <v>0.71</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
@@ -1096,13 +1096,13 @@
         <v>6</v>
       </c>
       <c r="C4" s="1">
-        <v>6.3879841463645004E-2</v>
+        <v>6.4170535590506894E-2</v>
       </c>
       <c r="D4" s="1">
-        <v>6.4899999999999999E-2</v>
+        <v>6.5199999999999994E-2</v>
       </c>
       <c r="E4">
-        <v>3.04</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
@@ -1113,13 +1113,13 @@
         <v>6</v>
       </c>
       <c r="C5" s="1">
-        <v>9.0741495259516913E-2</v>
+        <v>9.0358820872627366E-2</v>
       </c>
       <c r="D5" s="1">
-        <v>9.2799999999999994E-2</v>
+        <v>9.2399999999999996E-2</v>
       </c>
       <c r="E5">
-        <v>3.54</v>
+        <v>3.53</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
@@ -1130,13 +1130,13 @@
         <v>6</v>
       </c>
       <c r="C6" s="1">
-        <v>5.5918286313928256E-2</v>
+        <v>5.8057336421898587E-2</v>
       </c>
       <c r="D6" s="1">
-        <v>5.67E-2</v>
+        <v>5.8900000000000001E-2</v>
       </c>
       <c r="E6">
-        <v>3.13</v>
+        <v>3.26</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
@@ -1147,13 +1147,13 @@
         <v>6</v>
       </c>
       <c r="C7" s="1">
-        <v>4.7828117787232838E-2</v>
+        <v>4.8706909247879793E-2</v>
       </c>
       <c r="D7" s="1">
-        <v>4.8399999999999999E-2</v>
+        <v>4.9299999999999997E-2</v>
       </c>
       <c r="E7">
-        <v>1.08</v>
+        <v>1.1000000000000001</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
@@ -1164,10 +1164,10 @@
         <v>13</v>
       </c>
       <c r="C8" s="1">
-        <v>0.192</v>
+        <v>0.19</v>
       </c>
       <c r="D8" s="1">
-        <v>0.21160935225657296</v>
+        <v>0.2091898200018163</v>
       </c>
       <c r="E8">
         <v>5.5E-2</v>
@@ -1181,13 +1181,13 @@
         <v>13</v>
       </c>
       <c r="C9" s="1">
-        <v>0.24229999999999999</v>
+        <v>0.2505</v>
       </c>
       <c r="D9" s="1">
-        <v>0.26929999999999998</v>
+        <v>0.27879999999999999</v>
       </c>
       <c r="E9">
-        <v>0.14000000000000001</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
@@ -1198,13 +1198,13 @@
         <v>13</v>
       </c>
       <c r="C10" s="1">
-        <v>0.26412350379638594</v>
+        <v>0.26261004851892905</v>
       </c>
       <c r="D10" s="1">
-        <v>0.28899999999999998</v>
+        <v>0.28799999999999998</v>
       </c>
       <c r="E10">
-        <v>0.31</v>
+        <v>0.28999999999999998</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
@@ -1215,13 +1215,13 @@
         <v>13</v>
       </c>
       <c r="C11" s="1">
-        <v>0.26512677031170012</v>
+        <v>0.26777072020294224</v>
       </c>
       <c r="D11" s="1">
-        <v>0.29520000000000002</v>
+        <v>0.2989</v>
       </c>
       <c r="E11">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
@@ -1232,13 +1232,13 @@
         <v>6</v>
       </c>
       <c r="C12" s="1">
-        <v>6.6000000000000003E-2</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="D12" s="1">
-        <v>6.3E-2</v>
+        <v>6.7000000000000004E-2</v>
       </c>
       <c r="E12">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
@@ -1249,13 +1249,13 @@
         <v>19</v>
       </c>
       <c r="C13" s="1">
-        <v>8.3500000000000005E-2</v>
+        <v>8.6699999999999999E-2</v>
       </c>
       <c r="D13" s="1">
-        <v>8.2000000000000003E-2</v>
+        <v>8.5099999999999995E-2</v>
       </c>
       <c r="E13">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
@@ -1266,13 +1266,13 @@
         <v>13</v>
       </c>
       <c r="C14" s="1">
-        <v>0.29099999999999998</v>
+        <v>0.29749999999999999</v>
       </c>
       <c r="D14" s="1">
-        <v>0.29899999999999999</v>
+        <v>0.30499999999999999</v>
       </c>
       <c r="E14">
-        <v>0.79</v>
+        <v>0.82</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.3">
@@ -1286,10 +1286,10 @@
         <v>0.315</v>
       </c>
       <c r="D15" s="1">
-        <v>0.30199999999999999</v>
+        <v>0.3</v>
       </c>
       <c r="E15">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.3">
@@ -1300,10 +1300,10 @@
         <v>13</v>
       </c>
       <c r="C16" s="1">
-        <v>0.28499999999999998</v>
+        <v>0.27700000000000002</v>
       </c>
       <c r="D16" s="1">
-        <v>0.313</v>
+        <v>0.30359999999999998</v>
       </c>
       <c r="E16">
         <v>3.02</v>
@@ -1317,13 +1317,13 @@
         <v>13</v>
       </c>
       <c r="C17" s="1">
-        <v>0.22806018191709493</v>
+        <v>0.22490773891331303</v>
       </c>
       <c r="D17" s="1">
-        <v>0.24609713481414583</v>
+        <v>0.24279269417937288</v>
       </c>
       <c r="E17" s="2">
-        <v>0.32447791217453337</v>
+        <v>0.31227905037906428</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.3">
@@ -1334,13 +1334,13 @@
         <v>13</v>
       </c>
       <c r="C18" s="1">
-        <v>0.2896287908741888</v>
+        <v>0.29373058574890187</v>
       </c>
       <c r="D18" s="1">
-        <v>0.31059999999999999</v>
+        <v>0.31530000000000002</v>
       </c>
       <c r="E18">
-        <v>2.29</v>
+        <v>2.2599999999999998</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.3">
@@ -1351,10 +1351,10 @@
         <v>13</v>
       </c>
       <c r="C19" s="1">
-        <v>0.34195801639844087</v>
+        <v>0.33843593145357048</v>
       </c>
       <c r="D19" s="1">
-        <v>0.314</v>
+        <v>0.311</v>
       </c>
       <c r="E19">
         <v>1.59</v>
@@ -1410,13 +1410,13 @@
         <v>13</v>
       </c>
       <c r="C23" s="1">
-        <v>5.0073169425910891E-2</v>
+        <v>4.4896085379401374E-2</v>
       </c>
       <c r="D23" s="1">
-        <v>5.0700000000000002E-2</v>
+        <v>4.5400000000000003E-2</v>
       </c>
       <c r="E23">
-        <v>2.29</v>
+        <v>2.04</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.3">
@@ -1452,16 +1452,20 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="90" verticalDpi="90" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_Flow_SignoffStatus xmlns="c8a88c24-7513-4ed6-ad84-2b28824dfb6c" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="c8a88c24-7513-4ed6-ad84-2b28824dfb6c">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="b80a8b0a-2819-4368-b347-46490e6c629e" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1720,21 +1724,21 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_Flow_SignoffStatus xmlns="c8a88c24-7513-4ed6-ad84-2b28824dfb6c" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="c8a88c24-7513-4ed6-ad84-2b28824dfb6c">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="b80a8b0a-2819-4368-b347-46490e6c629e" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{226B4276-B5B3-4663-8452-863086008BD1}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{07D1F5F6-2D9A-42F8-BD5A-9CED205E0539}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="c8a88c24-7513-4ed6-ad84-2b28824dfb6c"/>
+    <ds:schemaRef ds:uri="b80a8b0a-2819-4368-b347-46490e6c629e"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -1759,12 +1763,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{07D1F5F6-2D9A-42F8-BD5A-9CED205E0539}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{226B4276-B5B3-4663-8452-863086008BD1}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="c8a88c24-7513-4ed6-ad84-2b28824dfb6c"/>
-    <ds:schemaRef ds:uri="b80a8b0a-2819-4368-b347-46490e6c629e"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/tir_fondos.xlsx
+++ b/tir_fondos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://balanzcapitalsa.sharepoint.com/sites/FCI/Shared Documents/General/FCI/Matias/Cartera de Fondos/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="55" documentId="8_{A13EEC8C-EB53-4E5F-A7CC-BE36694CDE73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F7BEB775-06C8-447A-8593-023C4E657355}"/>
+  <xr:revisionPtr revIDLastSave="92" documentId="8_{A13EEC8C-EB53-4E5F-A7CC-BE36694CDE73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BD55F194-4262-465D-942E-969C8362F0F4}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{9E9F1388-DBFD-43C1-B41D-53AD3C2134BF}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="32">
   <si>
     <t>fondo</t>
   </si>
@@ -126,9 +126,6 @@
   </si>
   <si>
     <t>Soja</t>
-  </si>
-  <si>
-    <t>-</t>
   </si>
   <si>
     <t>Latam Selection</t>
@@ -571,7 +568,7 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="42">
+  <cellStyleXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
@@ -614,13 +611,15 @@
     <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="42" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="42">
+  <cellStyles count="43">
     <cellStyle name="20% - Énfasis1" xfId="19" builtinId="30" customBuiltin="1"/>
     <cellStyle name="20% - Énfasis2" xfId="23" builtinId="34" customBuiltin="1"/>
     <cellStyle name="20% - Énfasis3" xfId="27" builtinId="38" customBuiltin="1"/>
@@ -656,6 +655,7 @@
     <cellStyle name="Neutral" xfId="8" builtinId="28" customBuiltin="1"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Notas" xfId="15" builtinId="10" customBuiltin="1"/>
+    <cellStyle name="Porcentaje" xfId="42" builtinId="5"/>
     <cellStyle name="Salida" xfId="10" builtinId="21" customBuiltin="1"/>
     <cellStyle name="Texto de advertencia" xfId="14" builtinId="11" customBuiltin="1"/>
     <cellStyle name="Texto explicativo" xfId="16" builtinId="53" customBuiltin="1"/>
@@ -1031,7 +1031,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B24BE737-EAE7-45F7-815A-66ACF5C2EE77}">
-  <dimension ref="A1:E25"/>
+  <dimension ref="A1:E26"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="21.88671875" bestFit="1" customWidth="1"/>
@@ -1062,10 +1062,10 @@
         <v>6</v>
       </c>
       <c r="C2" s="1">
-        <v>7.7999999999999996E-3</v>
+        <v>8.3000000000000001E-3</v>
       </c>
       <c r="D2" s="1">
-        <v>7.7999999999999996E-3</v>
+        <v>8.3000000000000001E-3</v>
       </c>
       <c r="E2">
         <v>0.06</v>
@@ -1079,13 +1079,13 @@
         <v>6</v>
       </c>
       <c r="C3" s="1">
-        <v>3.9117456155971286E-2</v>
+        <v>3.9313610016860512E-2</v>
       </c>
       <c r="D3" s="1">
-        <v>3.95E-2</v>
+        <v>3.9699999999999999E-2</v>
       </c>
       <c r="E3">
-        <v>0.7</v>
+        <v>0.65</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
@@ -1095,14 +1095,14 @@
       <c r="B4" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="1">
-        <v>6.4170535590506894E-2</v>
+      <c r="C4" s="3">
+        <v>6.5623392586363849E-2</v>
       </c>
       <c r="D4" s="1">
-        <v>6.5199999999999994E-2</v>
+        <v>6.6699999999999995E-2</v>
       </c>
       <c r="E4">
-        <v>3</v>
+        <v>3.01</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
@@ -1113,13 +1113,13 @@
         <v>6</v>
       </c>
       <c r="C5" s="1">
-        <v>9.0358820872627366E-2</v>
+        <v>9.0741495259516913E-2</v>
       </c>
       <c r="D5" s="1">
-        <v>9.2399999999999996E-2</v>
+        <v>9.2799999999999994E-2</v>
       </c>
       <c r="E5">
-        <v>3.53</v>
+        <v>3.49</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
@@ -1130,13 +1130,13 @@
         <v>6</v>
       </c>
       <c r="C6" s="1">
-        <v>5.8057336421898587E-2</v>
+        <v>5.9708717270478662E-2</v>
       </c>
       <c r="D6" s="1">
-        <v>5.8900000000000001E-2</v>
+        <v>6.0600000000000001E-2</v>
       </c>
       <c r="E6">
-        <v>3.26</v>
+        <v>3.28</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
@@ -1146,14 +1146,14 @@
       <c r="B7" t="s">
         <v>6</v>
       </c>
-      <c r="C7" s="1">
-        <v>4.8706909247879793E-2</v>
-      </c>
-      <c r="D7" s="1">
-        <v>4.9299999999999997E-2</v>
+      <c r="C7" s="3">
+        <v>5.1243525279239144E-2</v>
+      </c>
+      <c r="D7" s="3">
+        <v>5.1900000000000002E-2</v>
       </c>
       <c r="E7">
-        <v>1.1000000000000001</v>
+        <v>1.05</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
@@ -1163,14 +1163,14 @@
       <c r="B8" t="s">
         <v>13</v>
       </c>
-      <c r="C8" s="1">
-        <v>0.19</v>
-      </c>
-      <c r="D8" s="1">
-        <v>0.2091898200018163</v>
+      <c r="C8" s="3">
+        <v>0.19639999999999999</v>
+      </c>
+      <c r="D8" s="3">
+        <v>0.2169493315889619</v>
       </c>
       <c r="E8">
-        <v>5.5E-2</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
@@ -1180,14 +1180,14 @@
       <c r="B9" t="s">
         <v>13</v>
       </c>
-      <c r="C9" s="1">
-        <v>0.2505</v>
-      </c>
-      <c r="D9" s="1">
-        <v>0.27879999999999999</v>
+      <c r="C9" s="3">
+        <v>0.24110000000000001</v>
+      </c>
+      <c r="D9" s="3">
+        <v>0.26640000000000003</v>
       </c>
       <c r="E9">
-        <v>0.15</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
@@ -1197,14 +1197,14 @@
       <c r="B10" t="s">
         <v>13</v>
       </c>
-      <c r="C10" s="1">
-        <v>0.26261004851892905</v>
-      </c>
-      <c r="D10" s="1">
-        <v>0.28799999999999998</v>
+      <c r="C10" s="3">
+        <v>0.25856239643553686</v>
+      </c>
+      <c r="D10" s="3">
+        <v>0.28199999999999997</v>
       </c>
       <c r="E10">
-        <v>0.28999999999999998</v>
+        <v>0.32</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
@@ -1214,14 +1214,14 @@
       <c r="B11" t="s">
         <v>13</v>
       </c>
-      <c r="C11" s="1">
-        <v>0.26777072020294224</v>
-      </c>
-      <c r="D11" s="1">
-        <v>0.2989</v>
+      <c r="C11" s="3">
+        <v>0.26455896391050593</v>
+      </c>
+      <c r="D11" s="3">
+        <v>0.29449999999999998</v>
       </c>
       <c r="E11">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
@@ -1231,14 +1231,14 @@
       <c r="B12" t="s">
         <v>6</v>
       </c>
-      <c r="C12" s="1">
-        <v>7.0000000000000007E-2</v>
-      </c>
-      <c r="D12" s="1">
-        <v>6.7000000000000004E-2</v>
+      <c r="C12" s="3">
+        <v>5.1999999999999998E-2</v>
+      </c>
+      <c r="D12" s="3">
+        <v>5.1999999999999998E-2</v>
       </c>
       <c r="E12">
-        <v>0.8</v>
+        <v>0.84</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
@@ -1248,14 +1248,14 @@
       <c r="B13" t="s">
         <v>19</v>
       </c>
-      <c r="C13" s="1">
-        <v>8.6699999999999999E-2</v>
-      </c>
-      <c r="D13" s="1">
-        <v>8.5099999999999995E-2</v>
+      <c r="C13" s="3">
+        <v>0.08</v>
+      </c>
+      <c r="D13" s="3">
+        <v>7.8700000000000006E-2</v>
       </c>
       <c r="E13">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
@@ -1265,14 +1265,14 @@
       <c r="B14" t="s">
         <v>13</v>
       </c>
-      <c r="C14" s="1">
-        <v>0.29749999999999999</v>
-      </c>
-      <c r="D14" s="1">
-        <v>0.30499999999999999</v>
+      <c r="C14" s="3">
+        <v>0.29099999999999998</v>
+      </c>
+      <c r="D14" s="3">
+        <v>0.29899999999999999</v>
       </c>
       <c r="E14">
-        <v>0.82</v>
+        <v>0.81</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.3">
@@ -1282,14 +1282,14 @@
       <c r="B15" t="s">
         <v>13</v>
       </c>
-      <c r="C15" s="1">
+      <c r="C15" s="3">
         <v>0.315</v>
       </c>
-      <c r="D15" s="1">
-        <v>0.3</v>
+      <c r="D15" s="3">
+        <v>0.29799999999999999</v>
       </c>
       <c r="E15">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.3">
@@ -1299,14 +1299,14 @@
       <c r="B16" t="s">
         <v>13</v>
       </c>
-      <c r="C16" s="1">
-        <v>0.27700000000000002</v>
-      </c>
-      <c r="D16" s="1">
-        <v>0.30359999999999998</v>
-      </c>
-      <c r="E16">
-        <v>3.02</v>
+      <c r="C16" s="3">
+        <v>0.28100000000000003</v>
+      </c>
+      <c r="D16" s="3">
+        <v>0.3085</v>
+      </c>
+      <c r="E16" s="2">
+        <v>2.99</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.3">
@@ -1316,14 +1316,14 @@
       <c r="B17" t="s">
         <v>13</v>
       </c>
-      <c r="C17" s="1">
-        <v>0.22490773891331303</v>
-      </c>
-      <c r="D17" s="1">
-        <v>0.24279269417937288</v>
-      </c>
-      <c r="E17" s="2">
-        <v>0.31227905037906428</v>
+      <c r="C17" s="3">
+        <v>0.2358041258428151</v>
+      </c>
+      <c r="D17" s="3">
+        <v>0.25619999999999998</v>
+      </c>
+      <c r="E17">
+        <v>0.28999999999999998</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.3">
@@ -1333,14 +1333,14 @@
       <c r="B18" t="s">
         <v>13</v>
       </c>
-      <c r="C18" s="1">
-        <v>0.29373058574890187</v>
-      </c>
-      <c r="D18" s="1">
-        <v>0.31530000000000002</v>
+      <c r="C18" s="3">
+        <v>0.29041480959235866</v>
+      </c>
+      <c r="D18" s="3">
+        <v>0.3115</v>
       </c>
       <c r="E18">
-        <v>2.2599999999999998</v>
+        <v>2.25</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.3">
@@ -1350,11 +1350,11 @@
       <c r="B19" t="s">
         <v>13</v>
       </c>
-      <c r="C19" s="1">
-        <v>0.33843593145357048</v>
-      </c>
-      <c r="D19" s="1">
-        <v>0.311</v>
+      <c r="C19" s="3">
+        <v>0.32672999350229603</v>
+      </c>
+      <c r="D19" s="3">
+        <v>0.30099999999999999</v>
       </c>
       <c r="E19">
         <v>1.59</v>
@@ -1364,43 +1364,22 @@
       <c r="A20" t="s">
         <v>26</v>
       </c>
-      <c r="C20" t="s">
-        <v>31</v>
-      </c>
-      <c r="D20" t="s">
-        <v>31</v>
-      </c>
-      <c r="E20" t="s">
-        <v>31</v>
-      </c>
+      <c r="C20" s="3"/>
+      <c r="D20" s="3"/>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>27</v>
       </c>
-      <c r="C21" t="s">
-        <v>31</v>
-      </c>
-      <c r="D21" t="s">
-        <v>31</v>
-      </c>
-      <c r="E21" t="s">
-        <v>31</v>
-      </c>
+      <c r="C21" s="3"/>
+      <c r="D21" s="3"/>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>28</v>
       </c>
-      <c r="C22" t="s">
-        <v>31</v>
-      </c>
-      <c r="D22" t="s">
-        <v>31</v>
-      </c>
-      <c r="E22" t="s">
-        <v>31</v>
-      </c>
+      <c r="C22" s="3"/>
+      <c r="D22" s="3"/>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
@@ -1409,10 +1388,10 @@
       <c r="B23" t="s">
         <v>13</v>
       </c>
-      <c r="C23" s="1">
+      <c r="C23" s="3">
         <v>4.4896085379401374E-2</v>
       </c>
-      <c r="D23" s="1">
+      <c r="D23" s="3">
         <v>4.5400000000000003E-2</v>
       </c>
       <c r="E23">
@@ -1423,32 +1402,22 @@
       <c r="A24" t="s">
         <v>30</v>
       </c>
-      <c r="C24" t="s">
-        <v>31</v>
-      </c>
-      <c r="D24" t="s">
-        <v>31</v>
-      </c>
-      <c r="E24" t="s">
-        <v>31</v>
-      </c>
+      <c r="C24" s="3"/>
+      <c r="D24" s="3"/>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B25" t="s">
         <v>13</v>
       </c>
-      <c r="C25" s="1">
-        <v>0.22600000000000001</v>
-      </c>
-      <c r="D25" s="1">
-        <v>0.25339</v>
-      </c>
-      <c r="E25">
-        <v>0.01</v>
-      </c>
+      <c r="C25" s="3"/>
+      <c r="D25" s="3"/>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="C26" s="3"/>
+      <c r="D26" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1457,18 +1426,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_Flow_SignoffStatus xmlns="c8a88c24-7513-4ed6-ad84-2b28824dfb6c" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="c8a88c24-7513-4ed6-ad84-2b28824dfb6c">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="b80a8b0a-2819-4368-b347-46490e6c629e" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100365912C235D2A84A81A0B5F44B946490" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="48dbee4faefcea0cb3f303766da34021">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="c8a88c24-7513-4ed6-ad84-2b28824dfb6c" xmlns:ns3="b80a8b0a-2819-4368-b347-46490e6c629e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="e77cf793b771a80eba9682d9a8fa8d54" ns2:_="" ns3:_="">
     <xsd:import namespace="c8a88c24-7513-4ed6-ad84-2b28824dfb6c"/>
@@ -1723,7 +1680,7 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
@@ -1732,18 +1689,19 @@
 </FormTemplates>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{07D1F5F6-2D9A-42F8-BD5A-9CED205E0539}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="c8a88c24-7513-4ed6-ad84-2b28824dfb6c"/>
-    <ds:schemaRef ds:uri="b80a8b0a-2819-4368-b347-46490e6c629e"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_Flow_SignoffStatus xmlns="c8a88c24-7513-4ed6-ad84-2b28824dfb6c" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="c8a88c24-7513-4ed6-ad84-2b28824dfb6c">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="b80a8b0a-2819-4368-b347-46490e6c629e" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DD615DB7-24C1-4906-8C27-D5A5CB6996D7}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -1762,10 +1720,21 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{226B4276-B5B3-4663-8452-863086008BD1}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{07D1F5F6-2D9A-42F8-BD5A-9CED205E0539}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="c8a88c24-7513-4ed6-ad84-2b28824dfb6c"/>
+    <ds:schemaRef ds:uri="b80a8b0a-2819-4368-b347-46490e6c629e"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/tir_fondos.xlsx
+++ b/tir_fondos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://balanzcapitalsa.sharepoint.com/sites/FCI/Shared Documents/General/FCI/Matias/Cartera de Fondos/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="92" documentId="8_{A13EEC8C-EB53-4E5F-A7CC-BE36694CDE73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BD55F194-4262-465D-942E-969C8362F0F4}"/>
+  <xr:revisionPtr revIDLastSave="105" documentId="8_{A13EEC8C-EB53-4E5F-A7CC-BE36694CDE73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{93E4365C-C0E9-4CBD-9AA9-B978AFAC221E}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{9E9F1388-DBFD-43C1-B41D-53AD3C2134BF}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="33">
   <si>
     <t>fondo</t>
   </si>
@@ -129,6 +129,9 @@
   </si>
   <si>
     <t>Latam Selection</t>
+  </si>
+  <si>
+    <t>-</t>
   </si>
 </sst>
 </file>
@@ -613,10 +616,8 @@
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="42" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="43">
@@ -1062,10 +1063,10 @@
         <v>6</v>
       </c>
       <c r="C2" s="1">
-        <v>8.3000000000000001E-3</v>
+        <v>8.2000000000000007E-3</v>
       </c>
       <c r="D2" s="1">
-        <v>8.3000000000000001E-3</v>
+        <v>8.2000000000000007E-3</v>
       </c>
       <c r="E2">
         <v>0.06</v>
@@ -1079,13 +1080,13 @@
         <v>6</v>
       </c>
       <c r="C3" s="1">
-        <v>3.9313610016860512E-2</v>
+        <v>4.0392119177095953E-2</v>
       </c>
       <c r="D3" s="1">
-        <v>3.9699999999999999E-2</v>
+        <v>4.0800000000000003E-2</v>
       </c>
       <c r="E3">
-        <v>0.65</v>
+        <v>0.69</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
@@ -1095,14 +1096,14 @@
       <c r="B4" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="3">
-        <v>6.5623392586363849E-2</v>
+      <c r="C4" s="1">
+        <v>6.8235963327202054E-2</v>
       </c>
       <c r="D4" s="1">
-        <v>6.6699999999999995E-2</v>
+        <v>6.9400000000000003E-2</v>
       </c>
       <c r="E4">
-        <v>3.01</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
@@ -1113,13 +1114,13 @@
         <v>6</v>
       </c>
       <c r="C5" s="1">
-        <v>9.0741495259516913E-2</v>
+        <v>9.9523755521713664E-2</v>
       </c>
       <c r="D5" s="1">
-        <v>9.2799999999999994E-2</v>
+        <v>0.10199999999999999</v>
       </c>
       <c r="E5">
-        <v>3.49</v>
+        <v>3.45</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
@@ -1130,13 +1131,13 @@
         <v>6</v>
       </c>
       <c r="C6" s="1">
-        <v>5.9708717270478662E-2</v>
+        <v>6.0485379710324416E-2</v>
       </c>
       <c r="D6" s="1">
-        <v>6.0600000000000001E-2</v>
+        <v>6.1400000000000003E-2</v>
       </c>
       <c r="E6">
-        <v>3.28</v>
+        <v>3.22</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
@@ -1146,14 +1147,14 @@
       <c r="B7" t="s">
         <v>6</v>
       </c>
-      <c r="C7" s="3">
-        <v>5.1243525279239144E-2</v>
-      </c>
-      <c r="D7" s="3">
-        <v>5.1900000000000002E-2</v>
+      <c r="C7" s="1">
+        <v>6.1358775177188907E-2</v>
+      </c>
+      <c r="D7" s="1">
+        <v>6.2300000000000001E-2</v>
       </c>
       <c r="E7">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
@@ -1163,11 +1164,11 @@
       <c r="B8" t="s">
         <v>13</v>
       </c>
-      <c r="C8" s="3">
-        <v>0.19639999999999999</v>
-      </c>
-      <c r="D8" s="3">
-        <v>0.2169493315889619</v>
+      <c r="C8" s="1">
+        <v>0.1893</v>
+      </c>
+      <c r="D8" s="1">
+        <v>0.20834412257158896</v>
       </c>
       <c r="E8">
         <v>0.05</v>
@@ -1180,14 +1181,14 @@
       <c r="B9" t="s">
         <v>13</v>
       </c>
-      <c r="C9" s="3">
-        <v>0.24110000000000001</v>
-      </c>
-      <c r="D9" s="3">
-        <v>0.26640000000000003</v>
+      <c r="C9" s="1">
+        <v>0.23180000000000001</v>
+      </c>
+      <c r="D9" s="1">
+        <v>0.2545</v>
       </c>
       <c r="E9">
-        <v>0.18</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
@@ -1197,14 +1198,14 @@
       <c r="B10" t="s">
         <v>13</v>
       </c>
-      <c r="C10" s="3">
-        <v>0.25856239643553686</v>
-      </c>
-      <c r="D10" s="3">
-        <v>0.28199999999999997</v>
+      <c r="C10" s="1">
+        <v>0.25370497205289427</v>
+      </c>
+      <c r="D10" s="1">
+        <v>0.27700000000000002</v>
       </c>
       <c r="E10">
-        <v>0.32</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
@@ -1214,14 +1215,14 @@
       <c r="B11" t="s">
         <v>13</v>
       </c>
-      <c r="C11" s="3">
-        <v>0.26455896391050593</v>
-      </c>
-      <c r="D11" s="3">
-        <v>0.29449999999999998</v>
+      <c r="C11" s="1">
+        <v>0.26291958691153389</v>
+      </c>
+      <c r="D11" s="1">
+        <v>0.29289999999999999</v>
       </c>
       <c r="E11">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
@@ -1231,14 +1232,14 @@
       <c r="B12" t="s">
         <v>6</v>
       </c>
-      <c r="C12" s="3">
-        <v>5.1999999999999998E-2</v>
-      </c>
-      <c r="D12" s="3">
-        <v>5.1999999999999998E-2</v>
+      <c r="C12" s="1">
+        <v>6.6000000000000003E-2</v>
+      </c>
+      <c r="D12" s="1">
+        <v>6.6000000000000003E-2</v>
       </c>
       <c r="E12">
-        <v>0.84</v>
+        <v>0.87</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
@@ -1248,11 +1249,11 @@
       <c r="B13" t="s">
         <v>19</v>
       </c>
-      <c r="C13" s="3">
-        <v>0.08</v>
-      </c>
-      <c r="D13" s="3">
-        <v>7.8700000000000006E-2</v>
+      <c r="C13" s="1">
+        <v>9.0999999999999998E-2</v>
+      </c>
+      <c r="D13" s="1">
+        <v>8.8999999999999996E-2</v>
       </c>
       <c r="E13">
         <v>1.43</v>
@@ -1265,10 +1266,10 @@
       <c r="B14" t="s">
         <v>13</v>
       </c>
-      <c r="C14" s="3">
+      <c r="C14" s="1">
         <v>0.29099999999999998</v>
       </c>
-      <c r="D14" s="3">
+      <c r="D14" s="1">
         <v>0.29899999999999999</v>
       </c>
       <c r="E14">
@@ -1282,11 +1283,11 @@
       <c r="B15" t="s">
         <v>13</v>
       </c>
-      <c r="C15" s="3">
-        <v>0.315</v>
-      </c>
-      <c r="D15" s="3">
-        <v>0.29799999999999999</v>
+      <c r="C15" s="1">
+        <v>0.3097488081959614</v>
+      </c>
+      <c r="D15" s="1">
+        <v>0.29420000000000002</v>
       </c>
       <c r="E15">
         <v>1.38</v>
@@ -1299,13 +1300,13 @@
       <c r="B16" t="s">
         <v>13</v>
       </c>
-      <c r="C16" s="3">
-        <v>0.28100000000000003</v>
-      </c>
-      <c r="D16" s="3">
-        <v>0.3085</v>
-      </c>
-      <c r="E16" s="2">
+      <c r="C16" s="1">
+        <v>0.29199999999999998</v>
+      </c>
+      <c r="D16" s="1">
+        <v>0.32100000000000001</v>
+      </c>
+      <c r="E16">
         <v>2.99</v>
       </c>
     </row>
@@ -1316,14 +1317,14 @@
       <c r="B17" t="s">
         <v>13</v>
       </c>
-      <c r="C17" s="3">
-        <v>0.2358041258428151</v>
-      </c>
-      <c r="D17" s="3">
-        <v>0.25619999999999998</v>
+      <c r="C17" s="1">
+        <v>0.23965224805062432</v>
+      </c>
+      <c r="D17" s="1">
+        <v>0.26040000000000002</v>
       </c>
       <c r="E17">
-        <v>0.28999999999999998</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.3">
@@ -1333,14 +1334,14 @@
       <c r="B18" t="s">
         <v>13</v>
       </c>
-      <c r="C18" s="3">
-        <v>0.29041480959235866</v>
-      </c>
-      <c r="D18" s="3">
-        <v>0.3115</v>
+      <c r="C18" s="1">
+        <v>0.29294570367464212</v>
+      </c>
+      <c r="D18" s="1">
+        <v>0.31440000000000001</v>
       </c>
       <c r="E18">
-        <v>2.25</v>
+        <v>2.2200000000000002</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.3">
@@ -1350,11 +1351,11 @@
       <c r="B19" t="s">
         <v>13</v>
       </c>
-      <c r="C19" s="3">
-        <v>0.32672999350229603</v>
-      </c>
-      <c r="D19" s="3">
-        <v>0.30099999999999999</v>
+      <c r="C19" s="1">
+        <v>0.33140602206539754</v>
+      </c>
+      <c r="D19" s="1">
+        <v>0.30499999999999999</v>
       </c>
       <c r="E19">
         <v>1.59</v>
@@ -1364,22 +1365,43 @@
       <c r="A20" t="s">
         <v>26</v>
       </c>
-      <c r="C20" s="3"/>
-      <c r="D20" s="3"/>
+      <c r="C20" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="E20" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>27</v>
       </c>
-      <c r="C21" s="3"/>
-      <c r="D21" s="3"/>
+      <c r="C21" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="E21" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>28</v>
       </c>
-      <c r="C22" s="3"/>
-      <c r="D22" s="3"/>
+      <c r="C22" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="E22" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
@@ -1388,11 +1410,11 @@
       <c r="B23" t="s">
         <v>13</v>
       </c>
-      <c r="C23" s="3">
-        <v>4.4896085379401374E-2</v>
-      </c>
-      <c r="D23" s="3">
-        <v>4.5400000000000003E-2</v>
+      <c r="C23" s="1">
+        <v>4.4798278559525784E-2</v>
+      </c>
+      <c r="D23" s="1">
+        <v>4.53E-2</v>
       </c>
       <c r="E23">
         <v>2.04</v>
@@ -1402,8 +1424,15 @@
       <c r="A24" t="s">
         <v>30</v>
       </c>
-      <c r="C24" s="3"/>
-      <c r="D24" s="3"/>
+      <c r="C24" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="E24" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
@@ -1412,12 +1441,19 @@
       <c r="B25" t="s">
         <v>13</v>
       </c>
-      <c r="C25" s="3"/>
-      <c r="D25" s="3"/>
+      <c r="C25" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="E25" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="C26" s="3"/>
-      <c r="D26" s="3"/>
+      <c r="C26" s="1"/>
+      <c r="D26" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1426,6 +1462,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100365912C235D2A84A81A0B5F44B946490" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="48dbee4faefcea0cb3f303766da34021">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="c8a88c24-7513-4ed6-ad84-2b28824dfb6c" xmlns:ns3="b80a8b0a-2819-4368-b347-46490e6c629e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="e77cf793b771a80eba9682d9a8fa8d54" ns2:_="" ns3:_="">
     <xsd:import namespace="c8a88c24-7513-4ed6-ad84-2b28824dfb6c"/>
@@ -1680,15 +1725,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -1702,6 +1738,14 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{226B4276-B5B3-4663-8452-863086008BD1}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DD615DB7-24C1-4906-8C27-D5A5CB6996D7}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -1716,14 +1760,6 @@
     <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{226B4276-B5B3-4663-8452-863086008BD1}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/tir_fondos.xlsx
+++ b/tir_fondos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://balanzcapitalsa.sharepoint.com/sites/FCI/Shared Documents/General/FCI/Matias/Cartera de Fondos/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="105" documentId="8_{A13EEC8C-EB53-4E5F-A7CC-BE36694CDE73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{93E4365C-C0E9-4CBD-9AA9-B978AFAC221E}"/>
+  <xr:revisionPtr revIDLastSave="116" documentId="8_{A13EEC8C-EB53-4E5F-A7CC-BE36694CDE73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{44D8E312-C46D-46E2-A439-AF2D3648E839}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{9E9F1388-DBFD-43C1-B41D-53AD3C2134BF}"/>
   </bookViews>
@@ -1063,10 +1063,10 @@
         <v>6</v>
       </c>
       <c r="C2" s="1">
-        <v>8.2000000000000007E-3</v>
+        <v>8.5000000000000006E-3</v>
       </c>
       <c r="D2" s="1">
-        <v>8.2000000000000007E-3</v>
+        <v>8.5000000000000006E-3</v>
       </c>
       <c r="E2">
         <v>0.06</v>
@@ -1080,13 +1080,13 @@
         <v>6</v>
       </c>
       <c r="C3" s="1">
-        <v>4.0392119177095953E-2</v>
+        <v>3.764570031200476E-2</v>
       </c>
       <c r="D3" s="1">
-        <v>4.0800000000000003E-2</v>
+        <v>3.7999999999999999E-2</v>
       </c>
       <c r="E3">
-        <v>0.69</v>
+        <v>0.74</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
@@ -1097,13 +1097,13 @@
         <v>6</v>
       </c>
       <c r="C4" s="1">
-        <v>6.8235963327202054E-2</v>
+        <v>6.3298330343918074E-2</v>
       </c>
       <c r="D4" s="1">
-        <v>6.9400000000000003E-2</v>
+        <v>6.4299999999999996E-2</v>
       </c>
       <c r="E4">
-        <v>3</v>
+        <v>3.04</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
@@ -1114,13 +1114,13 @@
         <v>6</v>
       </c>
       <c r="C5" s="1">
-        <v>9.9523755521713664E-2</v>
+        <v>9.6282423720620791E-2</v>
       </c>
       <c r="D5" s="1">
-        <v>0.10199999999999999</v>
+        <v>9.8599999999999993E-2</v>
       </c>
       <c r="E5">
-        <v>3.45</v>
+        <v>3.57</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
@@ -1131,13 +1131,13 @@
         <v>6</v>
       </c>
       <c r="C6" s="1">
-        <v>6.0485379710324416E-2</v>
+        <v>6.358910638721893E-2</v>
       </c>
       <c r="D6" s="1">
-        <v>6.1400000000000003E-2</v>
+        <v>6.4600000000000005E-2</v>
       </c>
       <c r="E6">
-        <v>3.22</v>
+        <v>3.27</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
@@ -1148,13 +1148,13 @@
         <v>6</v>
       </c>
       <c r="C7" s="1">
-        <v>6.1358775177188907E-2</v>
+        <v>5.2608097031676238E-2</v>
       </c>
       <c r="D7" s="1">
-        <v>6.2300000000000001E-2</v>
+        <v>5.33E-2</v>
       </c>
       <c r="E7">
-        <v>1.03</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
@@ -1165,13 +1165,13 @@
         <v>13</v>
       </c>
       <c r="C8" s="1">
-        <v>0.1893</v>
+        <v>0.20349999999999999</v>
       </c>
       <c r="D8" s="1">
-        <v>0.20834412257158896</v>
+        <v>0.22561565341785661</v>
       </c>
       <c r="E8">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
@@ -1182,10 +1182,10 @@
         <v>13</v>
       </c>
       <c r="C9" s="1">
-        <v>0.23180000000000001</v>
+        <v>0.23250000000000001</v>
       </c>
       <c r="D9" s="1">
-        <v>0.2545</v>
+        <v>0.25530000000000003</v>
       </c>
       <c r="E9">
         <v>0.2</v>
@@ -1199,13 +1199,13 @@
         <v>13</v>
       </c>
       <c r="C10" s="1">
-        <v>0.25370497205289427</v>
+        <v>0.26345275392370315</v>
       </c>
       <c r="D10" s="1">
-        <v>0.27700000000000002</v>
+        <v>0.28699999999999998</v>
       </c>
       <c r="E10">
-        <v>0.3</v>
+        <v>0.34</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
@@ -1216,13 +1216,13 @@
         <v>13</v>
       </c>
       <c r="C11" s="1">
-        <v>0.26291958691153389</v>
+        <v>0.26985607389872213</v>
       </c>
       <c r="D11" s="1">
-        <v>0.29289999999999999</v>
+        <v>0.30059999999999998</v>
       </c>
       <c r="E11">
-        <v>0.18</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
@@ -1233,13 +1233,13 @@
         <v>6</v>
       </c>
       <c r="C12" s="1">
-        <v>6.6000000000000003E-2</v>
+        <v>6.5699999999999995E-2</v>
       </c>
       <c r="D12" s="1">
-        <v>6.6000000000000003E-2</v>
+        <v>6.5699999999999995E-2</v>
       </c>
       <c r="E12">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
@@ -1250,13 +1250,13 @@
         <v>19</v>
       </c>
       <c r="C13" s="1">
+        <v>9.2499999999999999E-2</v>
+      </c>
+      <c r="D13" s="1">
         <v>9.0999999999999998E-2</v>
       </c>
-      <c r="D13" s="1">
-        <v>8.8999999999999996E-2</v>
-      </c>
       <c r="E13">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
@@ -1270,10 +1270,10 @@
         <v>0.29099999999999998</v>
       </c>
       <c r="D14" s="1">
-        <v>0.29899999999999999</v>
+        <v>0.29949999999999999</v>
       </c>
       <c r="E14">
-        <v>0.81</v>
+        <v>0.78</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.3">
@@ -1284,13 +1284,13 @@
         <v>13</v>
       </c>
       <c r="C15" s="1">
-        <v>0.3097488081959614</v>
+        <v>0.34207550101814388</v>
       </c>
       <c r="D15" s="1">
-        <v>0.29420000000000002</v>
+        <v>0.31409999999999999</v>
       </c>
       <c r="E15">
-        <v>1.38</v>
+        <v>1.59</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.3">
@@ -1301,13 +1301,13 @@
         <v>13</v>
       </c>
       <c r="C16" s="1">
-        <v>0.29199999999999998</v>
+        <v>0.30059999999999998</v>
       </c>
       <c r="D16" s="1">
-        <v>0.32100000000000001</v>
+        <v>0.33139999999999997</v>
       </c>
       <c r="E16">
-        <v>2.99</v>
+        <v>2.95</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.3">
@@ -1318,13 +1318,13 @@
         <v>13</v>
       </c>
       <c r="C17" s="1">
-        <v>0.23965224805062432</v>
+        <v>0.22477800283172819</v>
       </c>
       <c r="D17" s="1">
-        <v>0.26040000000000002</v>
+        <v>0.24301837235579996</v>
       </c>
       <c r="E17">
-        <v>0.3</v>
+        <v>0.29917918245375391</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.3">
@@ -1335,13 +1335,13 @@
         <v>13</v>
       </c>
       <c r="C18" s="1">
-        <v>0.29294570367464212</v>
+        <v>0.29189877612428594</v>
       </c>
       <c r="D18" s="1">
-        <v>0.31440000000000001</v>
+        <v>0.31319999999999998</v>
       </c>
       <c r="E18">
-        <v>2.2200000000000002</v>
+        <v>2.19</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.3">
@@ -1352,13 +1352,13 @@
         <v>13</v>
       </c>
       <c r="C19" s="1">
-        <v>0.33140602206539754</v>
+        <v>0.36331478015278401</v>
       </c>
       <c r="D19" s="1">
-        <v>0.30499999999999999</v>
+        <v>0.32700000000000001</v>
       </c>
       <c r="E19">
-        <v>1.59</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.3">
@@ -1411,13 +1411,13 @@
         <v>13</v>
       </c>
       <c r="C23" s="1">
-        <v>4.4798278559525784E-2</v>
+        <v>5.2413213755943211E-2</v>
       </c>
       <c r="D23" s="1">
-        <v>4.53E-2</v>
+        <v>5.3100000000000001E-2</v>
       </c>
       <c r="E23">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.3">
@@ -1462,15 +1462,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100365912C235D2A84A81A0B5F44B946490" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="48dbee4faefcea0cb3f303766da34021">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="c8a88c24-7513-4ed6-ad84-2b28824dfb6c" xmlns:ns3="b80a8b0a-2819-4368-b347-46490e6c629e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="e77cf793b771a80eba9682d9a8fa8d54" ns2:_="" ns3:_="">
     <xsd:import namespace="c8a88c24-7513-4ed6-ad84-2b28824dfb6c"/>
@@ -1725,6 +1716,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -1738,14 +1738,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{226B4276-B5B3-4663-8452-863086008BD1}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DD615DB7-24C1-4906-8C27-D5A5CB6996D7}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -1760,6 +1752,14 @@
     <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{226B4276-B5B3-4663-8452-863086008BD1}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/tir_fondos.xlsx
+++ b/tir_fondos.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://balanzcapitalsa.sharepoint.com/sites/FCI/Shared Documents/General/FCI/Matias/Cartera de Fondos/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="116" documentId="8_{A13EEC8C-EB53-4E5F-A7CC-BE36694CDE73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{44D8E312-C46D-46E2-A439-AF2D3648E839}"/>
+  <xr:revisionPtr revIDLastSave="128" documentId="8_{A13EEC8C-EB53-4E5F-A7CC-BE36694CDE73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5D58259A-AC08-42FC-9713-FDF16549D283}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{9E9F1388-DBFD-43C1-B41D-53AD3C2134BF}"/>
   </bookViews>
   <sheets>
     <sheet name="tir_fondos" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029" iterateDelta="1E-4"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -616,9 +616,10 @@
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="42" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="43">
     <cellStyle name="20% - Énfasis1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -1063,12 +1064,12 @@
         <v>6</v>
       </c>
       <c r="C2" s="1">
-        <v>8.5000000000000006E-3</v>
+        <v>8.2000000000000007E-3</v>
       </c>
       <c r="D2" s="1">
-        <v>8.5000000000000006E-3</v>
-      </c>
-      <c r="E2">
+        <v>8.2000000000000007E-3</v>
+      </c>
+      <c r="E2" s="2">
         <v>0.06</v>
       </c>
     </row>
@@ -1080,12 +1081,12 @@
         <v>6</v>
       </c>
       <c r="C3" s="1">
-        <v>3.764570031200476E-2</v>
+        <v>3.5681703999915548E-2</v>
       </c>
       <c r="D3" s="1">
-        <v>3.7999999999999999E-2</v>
-      </c>
-      <c r="E3">
+        <v>3.5999999999999997E-2</v>
+      </c>
+      <c r="E3" s="2">
         <v>0.74</v>
       </c>
     </row>
@@ -1097,12 +1098,12 @@
         <v>6</v>
       </c>
       <c r="C4" s="1">
-        <v>6.3298330343918074E-2</v>
+        <v>6.39767440550294E-2</v>
       </c>
       <c r="D4" s="1">
-        <v>6.4299999999999996E-2</v>
-      </c>
-      <c r="E4">
+        <v>6.5000000000000002E-2</v>
+      </c>
+      <c r="E4" s="2">
         <v>3.04</v>
       </c>
     </row>
@@ -1114,13 +1115,13 @@
         <v>6</v>
       </c>
       <c r="C5" s="1">
-        <v>9.6282423720620791E-2</v>
+        <v>9.4850830011530718E-2</v>
       </c>
       <c r="D5" s="1">
-        <v>9.8599999999999993E-2</v>
-      </c>
-      <c r="E5">
-        <v>3.57</v>
+        <v>9.7100000000000006E-2</v>
+      </c>
+      <c r="E5" s="2">
+        <v>3.13</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
@@ -1131,13 +1132,13 @@
         <v>6</v>
       </c>
       <c r="C6" s="1">
-        <v>6.358910638721893E-2</v>
+        <v>6.39767440550294E-2</v>
       </c>
       <c r="D6" s="1">
-        <v>6.4600000000000005E-2</v>
-      </c>
-      <c r="E6">
-        <v>3.27</v>
+        <v>6.5000000000000002E-2</v>
+      </c>
+      <c r="E6" s="2">
+        <v>3.35</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
@@ -1148,13 +1149,13 @@
         <v>6</v>
       </c>
       <c r="C7" s="1">
-        <v>5.2608097031676238E-2</v>
+        <v>5.3582235996406435E-2</v>
       </c>
       <c r="D7" s="1">
-        <v>5.33E-2</v>
-      </c>
-      <c r="E7">
-        <v>1</v>
+        <v>5.4300000000000001E-2</v>
+      </c>
+      <c r="E7" s="2">
+        <v>1.0900000000000001</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
@@ -1165,13 +1166,13 @@
         <v>13</v>
       </c>
       <c r="C8" s="1">
-        <v>0.20349999999999999</v>
+        <v>0.1948</v>
       </c>
       <c r="D8" s="1">
-        <v>0.22561565341785661</v>
-      </c>
-      <c r="E8">
-        <v>0.04</v>
+        <v>0.21500481073975175</v>
+      </c>
+      <c r="E8" s="2">
+        <v>0.05</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
@@ -1182,12 +1183,12 @@
         <v>13</v>
       </c>
       <c r="C9" s="1">
-        <v>0.23250000000000001</v>
+        <v>0.24160000000000001</v>
       </c>
       <c r="D9" s="1">
-        <v>0.25530000000000003</v>
-      </c>
-      <c r="E9">
+        <v>0.26590000000000003</v>
+      </c>
+      <c r="E9" s="2">
         <v>0.2</v>
       </c>
     </row>
@@ -1199,13 +1200,13 @@
         <v>13</v>
       </c>
       <c r="C10" s="1">
-        <v>0.26345275392370315</v>
+        <v>0.25339126607693613</v>
       </c>
       <c r="D10" s="1">
-        <v>0.28699999999999998</v>
-      </c>
-      <c r="E10">
-        <v>0.34</v>
+        <v>0.27700000000000002</v>
+      </c>
+      <c r="E10" s="2">
+        <v>0.28999999999999998</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
@@ -1216,12 +1217,12 @@
         <v>13</v>
       </c>
       <c r="C11" s="1">
-        <v>0.26985607389872213</v>
+        <v>0.27341690007445685</v>
       </c>
       <c r="D11" s="1">
-        <v>0.30059999999999998</v>
-      </c>
-      <c r="E11">
+        <v>0.30499999999999999</v>
+      </c>
+      <c r="E11" s="2">
         <v>0.2</v>
       </c>
     </row>
@@ -1233,13 +1234,13 @@
         <v>6</v>
       </c>
       <c r="C12" s="1">
-        <v>6.5699999999999995E-2</v>
+        <v>5.5E-2</v>
       </c>
       <c r="D12" s="1">
-        <v>6.5699999999999995E-2</v>
-      </c>
-      <c r="E12">
-        <v>0.88</v>
+        <v>5.5E-2</v>
+      </c>
+      <c r="E12" s="2">
+        <v>0.97</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
@@ -1250,13 +1251,13 @@
         <v>19</v>
       </c>
       <c r="C13" s="1">
-        <v>9.2499999999999999E-2</v>
+        <v>8.2600000000000007E-2</v>
       </c>
       <c r="D13" s="1">
-        <v>9.0999999999999998E-2</v>
-      </c>
-      <c r="E13">
-        <v>1.4</v>
+        <v>8.14E-2</v>
+      </c>
+      <c r="E13" s="2">
+        <v>1.38</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
@@ -1267,13 +1268,13 @@
         <v>13</v>
       </c>
       <c r="C14" s="1">
-        <v>0.29099999999999998</v>
+        <v>0.26390000000000002</v>
       </c>
       <c r="D14" s="1">
-        <v>0.29949999999999999</v>
-      </c>
-      <c r="E14">
-        <v>0.78</v>
+        <v>0.2707</v>
+      </c>
+      <c r="E14" s="2">
+        <v>0.79</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.3">
@@ -1284,13 +1285,13 @@
         <v>13</v>
       </c>
       <c r="C15" s="1">
-        <v>0.34207550101814388</v>
+        <v>0.32079214971199327</v>
       </c>
       <c r="D15" s="1">
-        <v>0.31409999999999999</v>
-      </c>
-      <c r="E15">
-        <v>1.59</v>
+        <v>0.29899999999999999</v>
+      </c>
+      <c r="E15" s="2">
+        <v>1.51</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.3">
@@ -1301,13 +1302,13 @@
         <v>13</v>
       </c>
       <c r="C16" s="1">
-        <v>0.30059999999999998</v>
+        <v>0.29499999999999998</v>
       </c>
       <c r="D16" s="1">
-        <v>0.33139999999999997</v>
-      </c>
-      <c r="E16">
-        <v>2.95</v>
+        <v>0.32500000000000001</v>
+      </c>
+      <c r="E16" s="2">
+        <v>2.9</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.3">
@@ -1318,12 +1319,12 @@
         <v>13</v>
       </c>
       <c r="C17" s="1">
-        <v>0.22477800283172819</v>
+        <v>0.23247013439076172</v>
       </c>
       <c r="D17" s="1">
-        <v>0.24301837235579996</v>
-      </c>
-      <c r="E17">
+        <v>0.252</v>
+      </c>
+      <c r="E17" s="2">
         <v>0.29917918245375391</v>
       </c>
     </row>
@@ -1335,13 +1336,13 @@
         <v>13</v>
       </c>
       <c r="C18" s="1">
-        <v>0.29189877612428594</v>
+        <v>0.31698079405074076</v>
       </c>
       <c r="D18" s="1">
-        <v>0.31319999999999998</v>
-      </c>
-      <c r="E18">
-        <v>2.19</v>
+        <v>0.34210000000000002</v>
+      </c>
+      <c r="E18" s="2">
+        <v>2.16</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.3">
@@ -1352,13 +1353,13 @@
         <v>13</v>
       </c>
       <c r="C19" s="1">
-        <v>0.36331478015278401</v>
+        <v>0.3451559284605259</v>
       </c>
       <c r="D19" s="1">
-        <v>0.32700000000000001</v>
-      </c>
-      <c r="E19">
-        <v>1.7</v>
+        <v>0.315</v>
+      </c>
+      <c r="E19" s="2">
+        <v>1.63</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.3">
@@ -1371,7 +1372,7 @@
       <c r="D20" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="E20" t="s">
+      <c r="E20" s="2" t="s">
         <v>32</v>
       </c>
     </row>
@@ -1385,7 +1386,7 @@
       <c r="D21" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="E21" t="s">
+      <c r="E21" s="2" t="s">
         <v>32</v>
       </c>
     </row>
@@ -1399,7 +1400,7 @@
       <c r="D22" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="E22" t="s">
+      <c r="E22" s="2" t="s">
         <v>32</v>
       </c>
     </row>
@@ -1411,12 +1412,12 @@
         <v>13</v>
       </c>
       <c r="C23" s="1">
-        <v>5.2413213755943211E-2</v>
+        <v>5.2510657706799524E-2</v>
       </c>
       <c r="D23" s="1">
-        <v>5.3100000000000001E-2</v>
-      </c>
-      <c r="E23">
+        <v>5.3199999999999997E-2</v>
+      </c>
+      <c r="E23" s="2">
         <v>2.02</v>
       </c>
     </row>
@@ -1430,7 +1431,7 @@
       <c r="D24" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="E24" t="s">
+      <c r="E24" s="2" t="s">
         <v>32</v>
       </c>
     </row>
@@ -1447,13 +1448,14 @@
       <c r="D25" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="E25" t="s">
+      <c r="E25" s="2" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.3">
       <c r="C26" s="1"/>
       <c r="D26" s="1"/>
+      <c r="E26" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1462,6 +1464,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100365912C235D2A84A81A0B5F44B946490" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="48dbee4faefcea0cb3f303766da34021">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="c8a88c24-7513-4ed6-ad84-2b28824dfb6c" xmlns:ns3="b80a8b0a-2819-4368-b347-46490e6c629e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="e77cf793b771a80eba9682d9a8fa8d54" ns2:_="" ns3:_="">
     <xsd:import namespace="c8a88c24-7513-4ed6-ad84-2b28824dfb6c"/>
@@ -1716,15 +1727,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -1738,6 +1740,14 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{226B4276-B5B3-4663-8452-863086008BD1}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DD615DB7-24C1-4906-8C27-D5A5CB6996D7}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -1752,14 +1762,6 @@
     <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{226B4276-B5B3-4663-8452-863086008BD1}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/tir_fondos.xlsx
+++ b/tir_fondos.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://balanzcapitalsa.sharepoint.com/sites/FCI/Shared Documents/General/FCI/Matias/Cartera de Fondos/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="128" documentId="8_{A13EEC8C-EB53-4E5F-A7CC-BE36694CDE73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5D58259A-AC08-42FC-9713-FDF16549D283}"/>
+  <xr:revisionPtr revIDLastSave="137" documentId="8_{A13EEC8C-EB53-4E5F-A7CC-BE36694CDE73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{08F6F308-A1CE-4CA6-9BFA-F27AC827B98C}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{9E9F1388-DBFD-43C1-B41D-53AD3C2134BF}"/>
   </bookViews>
@@ -1064,10 +1064,10 @@
         <v>6</v>
       </c>
       <c r="C2" s="1">
-        <v>8.2000000000000007E-3</v>
+        <v>8.5000000000000006E-3</v>
       </c>
       <c r="D2" s="1">
-        <v>8.2000000000000007E-3</v>
+        <v>8.5000000000000006E-3</v>
       </c>
       <c r="E2" s="2">
         <v>0.06</v>
@@ -1081,13 +1081,13 @@
         <v>6</v>
       </c>
       <c r="C3" s="1">
-        <v>3.5681703999915548E-2</v>
+        <v>3.7743850438518578E-2</v>
       </c>
       <c r="D3" s="1">
-        <v>3.5999999999999997E-2</v>
+        <v>3.8100000000000002E-2</v>
       </c>
       <c r="E3" s="2">
-        <v>0.74</v>
+        <v>0.64</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
@@ -1098,13 +1098,13 @@
         <v>6</v>
       </c>
       <c r="C4" s="1">
-        <v>6.39767440550294E-2</v>
+        <v>6.3782934322309082E-2</v>
       </c>
       <c r="D4" s="1">
-        <v>6.5000000000000002E-2</v>
+        <v>6.4799999999999996E-2</v>
       </c>
       <c r="E4" s="2">
-        <v>3.04</v>
+        <v>3.13</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
@@ -1115,13 +1115,13 @@
         <v>6</v>
       </c>
       <c r="C5" s="1">
-        <v>9.4850830011530718E-2</v>
+        <v>9.5519028784992965E-2</v>
       </c>
       <c r="D5" s="1">
-        <v>9.7100000000000006E-2</v>
+        <v>9.7799999999999998E-2</v>
       </c>
       <c r="E5" s="2">
-        <v>3.13</v>
+        <v>3.06</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
@@ -1132,13 +1132,13 @@
         <v>6</v>
       </c>
       <c r="C6" s="1">
-        <v>6.39767440550294E-2</v>
+        <v>6.2037827005120505E-2</v>
       </c>
       <c r="D6" s="1">
-        <v>6.5000000000000002E-2</v>
+        <v>6.3E-2</v>
       </c>
       <c r="E6" s="2">
-        <v>3.35</v>
+        <v>3.19</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
@@ -1149,13 +1149,13 @@
         <v>6</v>
       </c>
       <c r="C7" s="1">
-        <v>5.3582235996406435E-2</v>
+        <v>5.0560898876207183E-2</v>
       </c>
       <c r="D7" s="1">
-        <v>5.4300000000000001E-2</v>
+        <v>5.1200000000000002E-2</v>
       </c>
       <c r="E7" s="2">
-        <v>1.0900000000000001</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
@@ -1166,10 +1166,10 @@
         <v>13</v>
       </c>
       <c r="C8" s="1">
-        <v>0.1948</v>
+        <v>0.19550000000000001</v>
       </c>
       <c r="D8" s="1">
-        <v>0.21500481073975175</v>
+        <v>0.21585515704968938</v>
       </c>
       <c r="E8" s="2">
         <v>0.05</v>
@@ -1183,10 +1183,10 @@
         <v>13</v>
       </c>
       <c r="C9" s="1">
-        <v>0.24160000000000001</v>
+        <v>0.24030000000000001</v>
       </c>
       <c r="D9" s="1">
-        <v>0.26590000000000003</v>
+        <v>0.26469999999999999</v>
       </c>
       <c r="E9" s="2">
         <v>0.2</v>
@@ -1200,13 +1200,13 @@
         <v>13</v>
       </c>
       <c r="C10" s="1">
-        <v>0.25339126607693613</v>
+        <v>0.25687235778129175</v>
       </c>
       <c r="D10" s="1">
-        <v>0.27700000000000002</v>
+        <v>0.28000000000000003</v>
       </c>
       <c r="E10" s="2">
-        <v>0.28999999999999998</v>
+        <v>0.32</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
@@ -1217,13 +1217,13 @@
         <v>13</v>
       </c>
       <c r="C11" s="1">
-        <v>0.27341690007445685</v>
+        <v>0.26845307135836149</v>
       </c>
       <c r="D11" s="1">
-        <v>0.30499999999999999</v>
+        <v>0.29799999999999999</v>
       </c>
       <c r="E11" s="2">
-        <v>0.2</v>
+        <v>0.22</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
@@ -1234,13 +1234,13 @@
         <v>6</v>
       </c>
       <c r="C12" s="1">
-        <v>5.5E-2</v>
+        <v>4.3999999999999997E-2</v>
       </c>
       <c r="D12" s="1">
-        <v>5.5E-2</v>
+        <v>4.3999999999999997E-2</v>
       </c>
       <c r="E12" s="2">
-        <v>0.97</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
@@ -1251,13 +1251,13 @@
         <v>19</v>
       </c>
       <c r="C13" s="1">
-        <v>8.2600000000000007E-2</v>
+        <v>8.0500000000000002E-2</v>
       </c>
       <c r="D13" s="1">
-        <v>8.14E-2</v>
+        <v>7.9500000000000001E-2</v>
       </c>
       <c r="E13" s="2">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
@@ -1268,13 +1268,13 @@
         <v>13</v>
       </c>
       <c r="C14" s="1">
-        <v>0.26390000000000002</v>
+        <v>0.29299999999999998</v>
       </c>
       <c r="D14" s="1">
-        <v>0.2707</v>
+        <v>0.30399999999999999</v>
       </c>
       <c r="E14" s="2">
-        <v>0.79</v>
+        <v>0.74</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.3">
@@ -1285,13 +1285,13 @@
         <v>13</v>
       </c>
       <c r="C15" s="1">
-        <v>0.32079214971199327</v>
+        <v>0.32767299929925231</v>
       </c>
       <c r="D15" s="1">
-        <v>0.29899999999999999</v>
+        <v>0.30299999999999999</v>
       </c>
       <c r="E15" s="2">
-        <v>1.51</v>
+        <v>1.56</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.3">
@@ -1302,10 +1302,10 @@
         <v>13</v>
       </c>
       <c r="C16" s="1">
-        <v>0.29499999999999998</v>
+        <v>0.29699999999999999</v>
       </c>
       <c r="D16" s="1">
-        <v>0.32500000000000001</v>
+        <v>0.32700000000000001</v>
       </c>
       <c r="E16" s="2">
         <v>2.9</v>
@@ -1336,13 +1336,13 @@
         <v>13</v>
       </c>
       <c r="C18" s="1">
-        <v>0.31698079405074076</v>
+        <v>0.31723973727363841</v>
       </c>
       <c r="D18" s="1">
-        <v>0.34210000000000002</v>
+        <v>0.34239999999999998</v>
       </c>
       <c r="E18" s="2">
-        <v>2.16</v>
+        <v>2.11</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.3">
@@ -1353,13 +1353,13 @@
         <v>13</v>
       </c>
       <c r="C19" s="1">
-        <v>0.3451559284605259</v>
+        <v>0.34359273525984302</v>
       </c>
       <c r="D19" s="1">
-        <v>0.315</v>
+        <v>0.312</v>
       </c>
       <c r="E19" s="2">
-        <v>1.63</v>
+        <v>1.67</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.3">
@@ -1464,15 +1464,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100365912C235D2A84A81A0B5F44B946490" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="48dbee4faefcea0cb3f303766da34021">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="c8a88c24-7513-4ed6-ad84-2b28824dfb6c" xmlns:ns3="b80a8b0a-2819-4368-b347-46490e6c629e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="e77cf793b771a80eba9682d9a8fa8d54" ns2:_="" ns3:_="">
     <xsd:import namespace="c8a88c24-7513-4ed6-ad84-2b28824dfb6c"/>
@@ -1727,6 +1718,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -1740,14 +1740,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{226B4276-B5B3-4663-8452-863086008BD1}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DD615DB7-24C1-4906-8C27-D5A5CB6996D7}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -1762,6 +1754,14 @@
     <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{226B4276-B5B3-4663-8452-863086008BD1}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/tir_fondos.xlsx
+++ b/tir_fondos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://balanzcapitalsa.sharepoint.com/sites/FCI/Shared Documents/General/FCI/Matias/Cartera de Fondos/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="137" documentId="8_{A13EEC8C-EB53-4E5F-A7CC-BE36694CDE73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{08F6F308-A1CE-4CA6-9BFA-F27AC827B98C}"/>
+  <xr:revisionPtr revIDLastSave="146" documentId="8_{A13EEC8C-EB53-4E5F-A7CC-BE36694CDE73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7016D1AE-ACAE-4FE6-B692-6497D490DE54}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{9E9F1388-DBFD-43C1-B41D-53AD3C2134BF}"/>
   </bookViews>
@@ -616,10 +616,11 @@
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="42" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="43">
     <cellStyle name="20% - Énfasis1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -1033,13 +1034,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B24BE737-EAE7-45F7-815A-66ACF5C2EE77}">
-  <dimension ref="A1:E26"/>
+  <dimension ref="A1:G26"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="21.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1056,7 +1057,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -1064,16 +1065,16 @@
         <v>6</v>
       </c>
       <c r="C2" s="1">
-        <v>8.5000000000000006E-3</v>
+        <v>7.9000000000000008E-3</v>
       </c>
       <c r="D2" s="1">
-        <v>8.5000000000000006E-3</v>
+        <v>7.9000000000000008E-3</v>
       </c>
       <c r="E2" s="2">
         <v>0.06</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>7</v>
       </c>
@@ -1081,16 +1082,16 @@
         <v>6</v>
       </c>
       <c r="C3" s="1">
-        <v>3.7743850438518578E-2</v>
+        <v>3.6663938896154491E-2</v>
       </c>
       <c r="D3" s="1">
-        <v>3.8100000000000002E-2</v>
+        <v>3.6999999999999998E-2</v>
       </c>
       <c r="E3" s="2">
-        <v>0.64</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+        <v>0.73</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>8</v>
       </c>
@@ -1098,16 +1099,16 @@
         <v>6</v>
       </c>
       <c r="C4" s="1">
-        <v>6.3782934322309082E-2</v>
+        <v>6.1843835017579618E-2</v>
       </c>
       <c r="D4" s="1">
-        <v>6.4799999999999996E-2</v>
+        <v>6.2799999999999995E-2</v>
       </c>
       <c r="E4" s="2">
-        <v>3.13</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+        <v>3.03</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>9</v>
       </c>
@@ -1115,16 +1116,16 @@
         <v>6</v>
       </c>
       <c r="C5" s="1">
-        <v>9.5519028784992965E-2</v>
+        <v>9.695016631297193E-2</v>
       </c>
       <c r="D5" s="1">
-        <v>9.7799999999999998E-2</v>
+        <v>9.9299999999999999E-2</v>
       </c>
       <c r="E5" s="2">
-        <v>3.06</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+        <v>2.98</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>10</v>
       </c>
@@ -1132,16 +1133,16 @@
         <v>6</v>
       </c>
       <c r="C6" s="1">
-        <v>6.2037827005120505E-2</v>
+        <v>6.1067684478120388E-2</v>
       </c>
       <c r="D6" s="1">
-        <v>6.3E-2</v>
+        <v>6.2E-2</v>
       </c>
       <c r="E6" s="2">
-        <v>3.19</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+        <v>3.35</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>11</v>
       </c>
@@ -1149,16 +1150,16 @@
         <v>6</v>
       </c>
       <c r="C7" s="1">
-        <v>5.0560898876207183E-2</v>
+        <v>5.1146021130626274E-2</v>
       </c>
       <c r="D7" s="1">
-        <v>5.1200000000000002E-2</v>
+        <v>5.1799999999999999E-2</v>
       </c>
       <c r="E7" s="2">
-        <v>0.99</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+        <v>0.98</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>12</v>
       </c>
@@ -1166,16 +1167,16 @@
         <v>13</v>
       </c>
       <c r="C8" s="1">
-        <v>0.19550000000000001</v>
+        <v>0.1978</v>
       </c>
       <c r="D8" s="1">
-        <v>0.21585515704968938</v>
+        <v>0.21865333301516676</v>
       </c>
       <c r="E8" s="2">
         <v>0.05</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>14</v>
       </c>
@@ -1183,16 +1184,16 @@
         <v>13</v>
       </c>
       <c r="C9" s="1">
-        <v>0.24030000000000001</v>
+        <v>0.24390000000000001</v>
       </c>
       <c r="D9" s="1">
-        <v>0.26469999999999999</v>
+        <v>0.26910000000000001</v>
       </c>
       <c r="E9" s="2">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+        <v>0.19</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>15</v>
       </c>
@@ -1200,16 +1201,16 @@
         <v>13</v>
       </c>
       <c r="C10" s="1">
-        <v>0.25687235778129175</v>
+        <v>0.25771760139147726</v>
       </c>
       <c r="D10" s="1">
-        <v>0.28000000000000003</v>
+        <v>0.28100000000000003</v>
       </c>
       <c r="E10" s="2">
         <v>0.32</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>16</v>
       </c>
@@ -1226,7 +1227,7 @@
         <v>0.22</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>17</v>
       </c>
@@ -1234,16 +1235,18 @@
         <v>6</v>
       </c>
       <c r="C12" s="1">
-        <v>4.3999999999999997E-2</v>
+        <v>5.5E-2</v>
       </c>
       <c r="D12" s="1">
-        <v>4.3999999999999997E-2</v>
+        <v>5.5E-2</v>
       </c>
       <c r="E12" s="2">
         <v>0.99</v>
       </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F12" s="3"/>
+      <c r="G12" s="3"/>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>18</v>
       </c>
@@ -1251,16 +1254,18 @@
         <v>19</v>
       </c>
       <c r="C13" s="1">
-        <v>8.0500000000000002E-2</v>
+        <v>7.6999999999999999E-2</v>
       </c>
       <c r="D13" s="1">
-        <v>7.9500000000000001E-2</v>
+        <v>7.6499999999999999E-2</v>
       </c>
       <c r="E13" s="2">
-        <v>1.35</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+        <v>1.32</v>
+      </c>
+      <c r="F13" s="3"/>
+      <c r="G13" s="3"/>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>20</v>
       </c>
@@ -1274,10 +1279,10 @@
         <v>0.30399999999999999</v>
       </c>
       <c r="E14" s="2">
-        <v>0.74</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+        <v>0.72</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>21</v>
       </c>
@@ -1285,16 +1290,16 @@
         <v>13</v>
       </c>
       <c r="C15" s="1">
-        <v>0.32767299929925231</v>
+        <v>0.33021099515649549</v>
       </c>
       <c r="D15" s="1">
-        <v>0.30299999999999999</v>
+        <v>0.30599999999999999</v>
       </c>
       <c r="E15" s="2">
-        <v>1.56</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+        <v>1.54</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>22</v>
       </c>
@@ -1336,13 +1341,13 @@
         <v>13</v>
       </c>
       <c r="C18" s="1">
-        <v>0.31723973727363841</v>
+        <v>0.31335254554942393</v>
       </c>
       <c r="D18" s="1">
-        <v>0.34239999999999998</v>
+        <v>0.33789999999999998</v>
       </c>
       <c r="E18" s="2">
-        <v>2.11</v>
+        <v>2.12</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.3">
@@ -1353,13 +1358,13 @@
         <v>13</v>
       </c>
       <c r="C19" s="1">
-        <v>0.34359273525984302</v>
+        <v>0.34736820859124695</v>
       </c>
       <c r="D19" s="1">
-        <v>0.312</v>
+        <v>0.316</v>
       </c>
       <c r="E19" s="2">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.3">
@@ -1412,13 +1417,13 @@
         <v>13</v>
       </c>
       <c r="C23" s="1">
-        <v>5.2510657706799524E-2</v>
+        <v>4.7242047243071017E-2</v>
       </c>
       <c r="D23" s="1">
-        <v>5.3199999999999997E-2</v>
+        <v>4.7800000000000002E-2</v>
       </c>
       <c r="E23" s="2">
-        <v>2.02</v>
+        <v>1.79</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.3">
@@ -1464,6 +1469,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100365912C235D2A84A81A0B5F44B946490" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="48dbee4faefcea0cb3f303766da34021">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="c8a88c24-7513-4ed6-ad84-2b28824dfb6c" xmlns:ns3="b80a8b0a-2819-4368-b347-46490e6c629e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="e77cf793b771a80eba9682d9a8fa8d54" ns2:_="" ns3:_="">
     <xsd:import namespace="c8a88c24-7513-4ed6-ad84-2b28824dfb6c"/>
@@ -1718,15 +1732,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -1740,6 +1745,14 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{226B4276-B5B3-4663-8452-863086008BD1}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DD615DB7-24C1-4906-8C27-D5A5CB6996D7}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -1754,14 +1767,6 @@
     <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{226B4276-B5B3-4663-8452-863086008BD1}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
